--- a/www/ig/fhir/cdl/ConceptMap-mos-cdl.xlsx
+++ b/www/ig/fhir/cdl/ConceptMap-mos-cdl.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="88">
   <si>
     <t>Property</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T16:22:12+00:00</t>
+    <t>2026-07-21T13:11:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -83,46 +83,49 @@
     <t>Jurisdiction</t>
   </si>
   <si>
+    <t>France (la)</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Mapping entre le MOS et les profils cahiers de liaison pour les profils qui ne sont pas présents dans ce guide.</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Donner un indice fonctionnel du mapping entre FHIR et MOS.</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Relationship</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/12.html</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Mapping entre le MOS et les profils cahiers de liaison pour les profils qui ne sont pas présents dans ce guide.</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Donner un indice fonctionnel du mapping entre FHIR et MOS.</t>
-  </si>
-  <si>
-    <t>Copyright</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr</t>
-  </si>
-  <si>
-    <t>Target</t>
-  </si>
-  <si>
-    <t>https://hl7.fr/ig/fhir/core</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Relationship</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/12.html</t>
-  </si>
-  <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|2.0.1</t>
   </si>
   <si>
     <t>Contact.IdContact</t>
@@ -158,7 +161,7 @@
     <t>RelatedPerson.name.given</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.0.1</t>
   </si>
   <si>
     <t>Professionnel.idPP</t>
@@ -194,7 +197,7 @@
     <t>PractitionerRole.code</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.0.1</t>
   </si>
   <si>
     <t>EntiteGeographique.numFINESS</t>
@@ -227,7 +230,7 @@
     <t>Organization.name</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.0.1</t>
   </si>
   <si>
     <t>PersonnePriseEnCharge.idPersonnePriseEnCharge</t>
@@ -266,7 +269,7 @@
     <t>Patient.name.given</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Device</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Device|4.0.1</t>
   </si>
   <si>
     <t>RessourceMaterielle.libelle</t>
@@ -577,101 +580,101 @@
         <v>33</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -706,101 +709,101 @@
         <v>33</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -835,33 +838,33 @@
         <v>33</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -896,101 +899,101 @@
         <v>33</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1025,152 +1028,152 @@
         <v>33</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1205,50 +1208,50 @@
         <v>33</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
